--- a/results/validation/onet_esco_crosswalk/onet_to_esco_match_summary.xlsx
+++ b/results/validation/onet_esco_crosswalk/onet_to_esco_match_summary.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gess-fs.d.ethz.ch\home$\fzaussinger\Documents\Projects\04_jrc_green-skills-regional\03_data-analysis\re4gt\results\validation\onet_esco_crosswalk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Documents\Projects\04_jrc_green-skills-regional\03_data-analysis\re4gt\results\validation\onet_esco_crosswalk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{D8D552BF-6DB1-4FA0-B48D-8AD66FC8074C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="-16320" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
@@ -1418,7 +1417,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1438,7 +1436,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E139" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:E139"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E139">
+  <sortState ref="A2:E139">
     <sortCondition descending="1" ref="E1:E139"/>
   </sortState>
   <tableColumns count="5">
@@ -1750,16 +1748,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E139"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.90625" customWidth="1"/>
-    <col min="2" max="2" width="83.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.08984375" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="83.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1776,7 +1774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1793,7 +1791,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1810,7 +1808,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1827,7 +1825,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1844,7 +1842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1861,7 +1859,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1878,7 +1876,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1895,7 +1893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1912,7 +1910,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1929,7 +1927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1946,7 +1944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1963,7 +1961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1980,7 +1978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1997,7 +1995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2014,7 +2012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2031,7 +2029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2048,7 +2046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2065,7 +2063,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2082,7 +2080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -2099,7 +2097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -2116,7 +2114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -2133,7 +2131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2150,7 +2148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -2167,7 +2165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -2184,7 +2182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -2201,7 +2199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -2218,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -2235,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2252,7 +2250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -2286,7 +2284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -2303,7 +2301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -2320,7 +2318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -2337,7 +2335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -2354,7 +2352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -2371,7 +2369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -2388,7 +2386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -2405,7 +2403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -2422,7 +2420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -2439,7 +2437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -2456,7 +2454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -2473,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -2490,7 +2488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -2507,7 +2505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>93</v>
       </c>
@@ -2524,7 +2522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -2541,7 +2539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -2558,7 +2556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>100</v>
       </c>
@@ -2575,7 +2573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -2592,7 +2590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -2609,7 +2607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>106</v>
       </c>
@@ -2626,7 +2624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>108</v>
       </c>
@@ -2643,7 +2641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>110</v>
       </c>
@@ -2660,7 +2658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>112</v>
       </c>
@@ -2677,7 +2675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>114</v>
       </c>
@@ -2694,7 +2692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>116</v>
       </c>
@@ -2711,7 +2709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -2728,7 +2726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>120</v>
       </c>
@@ -2745,7 +2743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>122</v>
       </c>
@@ -2762,7 +2760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>124</v>
       </c>
@@ -2779,7 +2777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>126</v>
       </c>
@@ -2796,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2813,7 +2811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -2830,7 +2828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>132</v>
       </c>
@@ -2847,7 +2845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>134</v>
       </c>
@@ -2864,7 +2862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>136</v>
       </c>
@@ -2881,7 +2879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -2898,7 +2896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>140</v>
       </c>
@@ -2915,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>142</v>
       </c>
@@ -2932,7 +2930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>144</v>
       </c>
@@ -2949,7 +2947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>146</v>
       </c>
@@ -2966,7 +2964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>148</v>
       </c>
@@ -2983,7 +2981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>150</v>
       </c>
@@ -3000,7 +2998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>152</v>
       </c>
@@ -3017,7 +3015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>154</v>
       </c>
@@ -3034,7 +3032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>156</v>
       </c>
@@ -3051,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>158</v>
       </c>
@@ -3068,7 +3066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>160</v>
       </c>
@@ -3085,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>162</v>
       </c>
@@ -3102,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>164</v>
       </c>
@@ -3119,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>166</v>
       </c>
@@ -3136,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>168</v>
       </c>
@@ -3153,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>170</v>
       </c>
@@ -3170,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>172</v>
       </c>
@@ -3187,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>174</v>
       </c>
@@ -3204,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>176</v>
       </c>
@@ -3221,7 +3219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>178</v>
       </c>
@@ -3238,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>180</v>
       </c>
@@ -3255,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>182</v>
       </c>
@@ -3272,7 +3270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>184</v>
       </c>
@@ -3289,7 +3287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>186</v>
       </c>
@@ -3306,7 +3304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>188</v>
       </c>
@@ -3323,7 +3321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>190</v>
       </c>
@@ -3340,7 +3338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>192</v>
       </c>
@@ -3357,7 +3355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>194</v>
       </c>
@@ -3374,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>196</v>
       </c>
@@ -3391,7 +3389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>198</v>
       </c>
@@ -3408,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>200</v>
       </c>
@@ -3425,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>202</v>
       </c>
@@ -3442,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -3459,7 +3457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>206</v>
       </c>
@@ -3476,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>208</v>
       </c>
@@ -3493,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -3510,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>212</v>
       </c>
@@ -3527,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>214</v>
       </c>
@@ -3544,7 +3542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>216</v>
       </c>
@@ -3561,7 +3559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>218</v>
       </c>
@@ -3578,7 +3576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>220</v>
       </c>
@@ -3595,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>222</v>
       </c>
@@ -3612,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>224</v>
       </c>
@@ -3629,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>226</v>
       </c>
@@ -3646,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>228</v>
       </c>
@@ -3663,7 +3661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>230</v>
       </c>
@@ -3680,7 +3678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>232</v>
       </c>
@@ -3697,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>234</v>
       </c>
@@ -3714,7 +3712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>236</v>
       </c>
@@ -3731,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>238</v>
       </c>
@@ -3748,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>240</v>
       </c>
@@ -3765,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>242</v>
       </c>
@@ -3782,7 +3780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>244</v>
       </c>
@@ -3799,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>246</v>
       </c>
@@ -3816,7 +3814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>248</v>
       </c>
@@ -3833,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>250</v>
       </c>
@@ -3850,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>252</v>
       </c>
@@ -3867,7 +3865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>254</v>
       </c>
@@ -3884,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>256</v>
       </c>
@@ -3901,7 +3899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>258</v>
       </c>
@@ -3918,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>260</v>
       </c>
@@ -3935,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>262</v>
       </c>
@@ -3952,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>264</v>
       </c>
@@ -3969,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>266</v>
       </c>
@@ -3986,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>268</v>
       </c>
@@ -4003,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>270</v>
       </c>
@@ -4020,7 +4018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>272</v>
       </c>
@@ -4037,7 +4035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>274</v>
       </c>
@@ -4054,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>276</v>
       </c>
@@ -4071,7 +4069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>278</v>
       </c>
@@ -4088,7 +4086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>280</v>
       </c>
@@ -4105,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>282</v>
       </c>

--- a/results/validation/onet_esco_crosswalk/onet_to_esco_match_summary.xlsx
+++ b/results/validation/onet_esco_crosswalk/onet_to_esco_match_summary.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Documents\Projects\04_jrc_green-skills-regional\03_data-analysis\re4gt\results\validation\onet_esco_crosswalk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gess-fs.d.ethz.ch\home$\fzaussinger\Documents\Projects\04_jrc_green-skills-regional\03_data-analysis\re4gt\results\validation\onet_esco_crosswalk\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1B1B88-E15C-479C-AA41-868772A8CD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-16320" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="onet_to_esco_match_summary" sheetId="1" r:id="rId1"/>
@@ -876,7 +877,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1434,17 +1435,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E139" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:E139"/>
-  <sortState ref="A2:E139">
-    <sortCondition descending="1" ref="E1:E139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:E139" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:E139" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E139">
+    <sortCondition ref="E1:E139"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="onet_code"/>
-    <tableColumn id="2" name="title_gtp"/>
-    <tableColumn id="3" name="occupation_type"/>
-    <tableColumn id="4" name="share_green_gtp"/>
-    <tableColumn id="5" name="n_matches_esco"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="onet_code"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="title_gtp"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="occupation_type"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="share_green_gtp"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="n_matches_esco"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1746,18 +1747,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="83.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="83.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1774,794 +1775,794 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>0.13793103400000001</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>0.1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>0.366666667</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>0.133333333</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13">
         <v>0.3</v>
       </c>
-      <c r="E2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>0.28571428599999998</v>
-      </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>4.7619047999999997E-2</v>
-      </c>
-      <c r="E4">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>3.5714285999999998E-2</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>0.33333333300000001</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>0.19047618999999999</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>0.14285714299999999</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>0.3</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>0.428571429</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>214</v>
+      </c>
+      <c r="B30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>216</v>
+      </c>
+      <c r="B31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31">
+        <v>0.23809523799999999</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>218</v>
+      </c>
+      <c r="B32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32">
+        <v>0.42105263199999998</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33">
+        <v>8.3333332999999996E-2</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>222</v>
+      </c>
+      <c r="B34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34">
+        <v>0.17391304299999999</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35">
+        <v>0.27777777799999998</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>226</v>
+      </c>
+      <c r="B36" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36">
+        <v>0.105263158</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>8.3333332999999996E-2</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" t="s">
+        <v>231</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38">
         <v>0.2</v>
       </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8">
-        <v>0.22727272700000001</v>
-      </c>
-      <c r="E8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>0.13513513499999999</v>
-      </c>
-      <c r="E9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10">
-        <v>0.48387096800000001</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>0.47058823500000002</v>
-      </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>0.14285714299999999</v>
-      </c>
-      <c r="E12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>0.20833333300000001</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14">
-        <v>9.0909090999999997E-2</v>
-      </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>0.33333333300000001</v>
-      </c>
-      <c r="E15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16">
-        <v>9.0909090999999997E-2</v>
-      </c>
-      <c r="E16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18">
-        <v>0.117647059</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>0.18181818199999999</v>
-      </c>
-      <c r="E19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20">
-        <v>0.222222222</v>
-      </c>
-      <c r="E20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22">
-        <v>0.30769230800000003</v>
-      </c>
-      <c r="E22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23">
-        <v>9.6774193999999994E-2</v>
-      </c>
-      <c r="E23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24">
-        <v>0.25</v>
-      </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25">
-        <v>0.15</v>
-      </c>
-      <c r="E25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26">
-        <v>0.14814814800000001</v>
-      </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27">
-        <v>0.5</v>
-      </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28">
-        <v>6.8965517000000004E-2</v>
-      </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29">
-        <v>0.26315789499999998</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32">
-        <v>0.115384615</v>
-      </c>
-      <c r="E32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33">
-        <v>0.30434782599999999</v>
-      </c>
-      <c r="E33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34">
-        <v>0.3125</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35">
-        <v>0.21428571399999999</v>
-      </c>
-      <c r="E35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36">
-        <v>0.20833333300000001</v>
-      </c>
-      <c r="E36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37">
-        <v>0.133333333</v>
-      </c>
-      <c r="E37">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38">
-        <v>0.21739130400000001</v>
-      </c>
       <c r="E38">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
       </c>
       <c r="D39">
-        <v>0.16666666699999999</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>234</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D40">
-        <v>4.7619047999999997E-2</v>
+        <v>0.35294117600000002</v>
       </c>
       <c r="E40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>236</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>237</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
       </c>
       <c r="D41">
-        <v>0.34285714299999998</v>
+        <v>0.15789473700000001</v>
       </c>
       <c r="E41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>238</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.368421053</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D43">
-        <v>0.192307692</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>243</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>244</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>245</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D45">
-        <v>0.30434782599999999</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D46">
-        <v>0.222222222</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="E47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="C48" t="s">
         <v>99</v>
@@ -2570,168 +2571,168 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0.117647059</v>
       </c>
       <c r="E49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="C50" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D50">
-        <v>9.0909090999999997E-2</v>
+        <v>0.2</v>
       </c>
       <c r="E50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>106</v>
+        <v>256</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D51">
-        <v>0.18181818199999999</v>
+        <v>0.130434783</v>
       </c>
       <c r="E51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>258</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
       <c r="D52">
-        <v>0.39130434800000002</v>
+        <v>0.368421053</v>
       </c>
       <c r="E52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
       </c>
       <c r="D53">
-        <v>0.25</v>
+        <v>0.17647058800000001</v>
       </c>
       <c r="E53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0.32</v>
       </c>
       <c r="E55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>116</v>
+        <v>266</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D56">
-        <v>0.26923076899999998</v>
+        <v>0.31818181800000001</v>
       </c>
       <c r="E56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>269</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>271</v>
       </c>
       <c r="C58" t="s">
         <v>99</v>
@@ -2740,321 +2741,321 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>272</v>
+      </c>
+      <c r="B59" t="s">
+        <v>273</v>
+      </c>
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59">
+        <v>0.25</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>274</v>
+      </c>
+      <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60">
+        <v>0.5</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>276</v>
+      </c>
+      <c r="B61" t="s">
+        <v>277</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61">
+        <v>0.26315789499999998</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>278</v>
+      </c>
+      <c r="B62" t="s">
+        <v>279</v>
+      </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62">
+        <v>8.3333332999999996E-2</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>280</v>
+      </c>
+      <c r="B63" t="s">
+        <v>281</v>
+      </c>
+      <c r="C63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>282</v>
+      </c>
+      <c r="B64" t="s">
+        <v>283</v>
+      </c>
+      <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64">
+        <v>0.17391304299999999</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>118</v>
+      </c>
+      <c r="B65" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>122</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B67" t="s">
         <v>123</v>
       </c>
-      <c r="C59" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59">
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67">
         <v>0.15</v>
       </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="E67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>124</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B68" t="s">
         <v>125</v>
       </c>
-      <c r="C60" t="s">
-        <v>32</v>
-      </c>
-      <c r="D60">
+      <c r="C68" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68">
         <v>0.2</v>
       </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>126</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B69" t="s">
         <v>127</v>
       </c>
-      <c r="C61" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61">
+      <c r="C69" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69">
         <v>0.13636363600000001</v>
       </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>128</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B70" t="s">
         <v>129</v>
       </c>
-      <c r="C62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62">
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70">
         <v>0.46153846199999998</v>
       </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>130</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B71" t="s">
         <v>131</v>
       </c>
-      <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63">
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71">
         <v>5.2631578999999998E-2</v>
       </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>132</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B72" t="s">
         <v>133</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C72" t="s">
         <v>99</v>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>134</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B73" t="s">
         <v>135</v>
       </c>
-      <c r="C65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65">
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73">
         <v>0.34615384599999999</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="E73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>136</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B74" t="s">
         <v>137</v>
       </c>
-      <c r="C66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66">
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74">
         <v>0.321428571</v>
       </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>138</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B75" t="s">
         <v>139</v>
       </c>
-      <c r="C67" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67">
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75">
         <v>0.13636363600000001</v>
       </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="E75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>140</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B76" t="s">
         <v>141</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C76" t="s">
         <v>99</v>
       </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>142</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B77" t="s">
         <v>143</v>
-      </c>
-      <c r="C69" t="s">
-        <v>99</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" t="s">
-        <v>145</v>
-      </c>
-      <c r="C70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D70">
-        <v>9.0909090999999997E-2</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" t="s">
-        <v>147</v>
-      </c>
-      <c r="C71" t="s">
-        <v>32</v>
-      </c>
-      <c r="D71">
-        <v>0.1875</v>
-      </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>148</v>
-      </c>
-      <c r="B72" t="s">
-        <v>149</v>
-      </c>
-      <c r="C72" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72">
-        <v>0.20689655200000001</v>
-      </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>150</v>
-      </c>
-      <c r="B73" t="s">
-        <v>151</v>
-      </c>
-      <c r="C73" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73">
-        <v>0.31034482800000002</v>
-      </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>152</v>
-      </c>
-      <c r="B74" t="s">
-        <v>153</v>
-      </c>
-      <c r="C74" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74">
-        <v>0.25</v>
-      </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>154</v>
-      </c>
-      <c r="B75" t="s">
-        <v>155</v>
-      </c>
-      <c r="C75" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75">
-        <v>0.19354838699999999</v>
-      </c>
-      <c r="E75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>156</v>
-      </c>
-      <c r="B76" t="s">
-        <v>157</v>
-      </c>
-      <c r="C76" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76">
-        <v>0.17391304299999999</v>
-      </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" t="s">
-        <v>159</v>
       </c>
       <c r="C77" t="s">
         <v>99</v>
@@ -3063,389 +3064,389 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C78" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78">
+        <v>9.0909090999999997E-2</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>146</v>
+      </c>
+      <c r="B79" t="s">
+        <v>147</v>
+      </c>
+      <c r="C79" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79">
+        <v>0.1875</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" t="s">
+        <v>149</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80">
+        <v>0.20689655200000001</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" t="s">
+        <v>151</v>
+      </c>
+      <c r="C81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81">
+        <v>0.31034482800000002</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>0.25</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>154</v>
+      </c>
+      <c r="B83" t="s">
+        <v>155</v>
+      </c>
+      <c r="C83" t="s">
+        <v>32</v>
+      </c>
+      <c r="D83">
+        <v>0.19354838699999999</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" t="s">
+        <v>157</v>
+      </c>
+      <c r="C84" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84">
+        <v>0.17391304299999999</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85">
+        <v>4.7619047999999997E-2</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
+        <v>32</v>
+      </c>
+      <c r="D86">
+        <v>0.34285714299999998</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87">
+        <v>0.368421053</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" t="s">
+        <v>90</v>
+      </c>
+      <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88">
+        <v>0.192307692</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" t="s">
+        <v>92</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90">
+        <v>0.30434782599999999</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91">
+        <v>0.222222222</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92" t="s">
         <v>99</v>
       </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" t="s">
-        <v>163</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" t="s">
+        <v>101</v>
+      </c>
+      <c r="C93" t="s">
         <v>99</v>
       </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>164</v>
-      </c>
-      <c r="B80" t="s">
-        <v>165</v>
-      </c>
-      <c r="C80" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80">
-        <v>0.13793103400000001</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>166</v>
-      </c>
-      <c r="B81" t="s">
-        <v>167</v>
-      </c>
-      <c r="C81" t="s">
-        <v>99</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>168</v>
-      </c>
-      <c r="B82" t="s">
-        <v>169</v>
-      </c>
-      <c r="C82" t="s">
-        <v>99</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>170</v>
-      </c>
-      <c r="B83" t="s">
-        <v>171</v>
-      </c>
-      <c r="C83" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83">
-        <v>0.1</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>172</v>
-      </c>
-      <c r="B84" t="s">
-        <v>173</v>
-      </c>
-      <c r="C84" t="s">
-        <v>32</v>
-      </c>
-      <c r="D84">
-        <v>0.366666667</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>174</v>
-      </c>
-      <c r="B85" t="s">
-        <v>175</v>
-      </c>
-      <c r="C85" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85">
-        <v>0.133333333</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>176</v>
-      </c>
-      <c r="B86" t="s">
-        <v>177</v>
-      </c>
-      <c r="C86" t="s">
-        <v>99</v>
-      </c>
-      <c r="D86">
-        <v>1</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>178</v>
-      </c>
-      <c r="B87" t="s">
-        <v>179</v>
-      </c>
-      <c r="C87" t="s">
-        <v>99</v>
-      </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>180</v>
-      </c>
-      <c r="B88" t="s">
-        <v>181</v>
-      </c>
-      <c r="C88" t="s">
-        <v>32</v>
-      </c>
-      <c r="D88">
-        <v>0.3</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>182</v>
-      </c>
-      <c r="B89" t="s">
-        <v>183</v>
-      </c>
-      <c r="C89" t="s">
-        <v>32</v>
-      </c>
-      <c r="D89">
-        <v>0.33333333300000001</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>184</v>
-      </c>
-      <c r="B90" t="s">
-        <v>185</v>
-      </c>
-      <c r="C90" t="s">
-        <v>99</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>186</v>
-      </c>
-      <c r="B91" t="s">
-        <v>187</v>
-      </c>
-      <c r="C91" t="s">
-        <v>99</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>188</v>
-      </c>
-      <c r="B92" t="s">
-        <v>189</v>
-      </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92">
-        <v>0.19047618999999999</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>190</v>
-      </c>
-      <c r="B93" t="s">
-        <v>191</v>
-      </c>
-      <c r="C93" t="s">
-        <v>7</v>
-      </c>
       <c r="D93">
-        <v>0.14285714299999999</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="B94" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="C94" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D94">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="B95" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="C95" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>9.0909090999999997E-2</v>
       </c>
       <c r="E95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="C96" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0.18181818199999999</v>
       </c>
       <c r="E96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0.39130434800000002</v>
       </c>
       <c r="E97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="C99" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="C100" t="s">
         <v>99</v>
@@ -3454,670 +3455,670 @@
         <v>1</v>
       </c>
       <c r="E100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="C101" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0.26923076899999998</v>
       </c>
       <c r="E101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="B102" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="C102" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0.3125</v>
       </c>
       <c r="E102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="C103" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0.21428571399999999</v>
       </c>
       <c r="E103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="C104" t="s">
         <v>7</v>
       </c>
       <c r="D104">
-        <v>0.428571429</v>
+        <v>0.20833333300000001</v>
       </c>
       <c r="E104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="B105" t="s">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="C105" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0.133333333</v>
       </c>
       <c r="E105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="B106" t="s">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="C106" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D106">
-        <v>0.23809523799999999</v>
+        <v>0.21739130400000001</v>
       </c>
       <c r="E106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="C107" t="s">
         <v>32</v>
       </c>
       <c r="D107">
-        <v>0.42105263199999998</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="E107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="B108" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D108">
-        <v>8.3333332999999996E-2</v>
+        <v>0.26315789499999998</v>
       </c>
       <c r="E108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="B109" t="s">
-        <v>223</v>
+        <v>64</v>
       </c>
       <c r="C109" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D109">
-        <v>0.17391304299999999</v>
+        <v>1</v>
       </c>
       <c r="E109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="B110" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="C110" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D110">
-        <v>0.27777777799999998</v>
+        <v>1</v>
       </c>
       <c r="E110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>226</v>
+        <v>67</v>
       </c>
       <c r="B111" t="s">
-        <v>227</v>
+        <v>68</v>
       </c>
       <c r="C111" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D111">
-        <v>0.105263158</v>
+        <v>0.115384615</v>
       </c>
       <c r="E111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>228</v>
+        <v>69</v>
       </c>
       <c r="B112" t="s">
-        <v>229</v>
+        <v>70</v>
       </c>
       <c r="C112" t="s">
         <v>7</v>
       </c>
       <c r="D112">
-        <v>8.3333332999999996E-2</v>
+        <v>0.30434782599999999</v>
       </c>
       <c r="E112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>230</v>
+        <v>51</v>
       </c>
       <c r="B113" t="s">
-        <v>231</v>
+        <v>52</v>
       </c>
       <c r="C113" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D113">
+        <v>0.25</v>
+      </c>
+      <c r="E113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>53</v>
+      </c>
+      <c r="B114" t="s">
+        <v>54</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114">
+        <v>0.15</v>
+      </c>
+      <c r="E114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>55</v>
+      </c>
+      <c r="B115" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115">
+        <v>0.14814814800000001</v>
+      </c>
+      <c r="E115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>57</v>
+      </c>
+      <c r="B116" t="s">
+        <v>58</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116">
+        <v>0.5</v>
+      </c>
+      <c r="E116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>59</v>
+      </c>
+      <c r="B117" t="s">
+        <v>60</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117">
+        <v>6.8965517000000004E-2</v>
+      </c>
+      <c r="E117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>45</v>
+      </c>
+      <c r="B118" t="s">
+        <v>46</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>47</v>
+      </c>
+      <c r="B119" t="s">
+        <v>48</v>
+      </c>
+      <c r="C119" t="s">
+        <v>32</v>
+      </c>
+      <c r="D119">
+        <v>0.30769230800000003</v>
+      </c>
+      <c r="E119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>49</v>
+      </c>
+      <c r="B120" t="s">
+        <v>50</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120">
+        <v>9.6774193999999994E-2</v>
+      </c>
+      <c r="E120">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>39</v>
+      </c>
+      <c r="B121" t="s">
+        <v>40</v>
+      </c>
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121">
+        <v>0.117647059</v>
+      </c>
+      <c r="E121">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>41</v>
+      </c>
+      <c r="B122" t="s">
+        <v>42</v>
+      </c>
+      <c r="C122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122">
+        <v>0.18181818199999999</v>
+      </c>
+      <c r="E122">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>43</v>
+      </c>
+      <c r="B123" t="s">
+        <v>44</v>
+      </c>
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123">
+        <v>0.222222222</v>
+      </c>
+      <c r="E123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124">
+        <v>0.33333333300000001</v>
+      </c>
+      <c r="E124">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>35</v>
+      </c>
+      <c r="B125" t="s">
+        <v>36</v>
+      </c>
+      <c r="C125" t="s">
+        <v>32</v>
+      </c>
+      <c r="D125">
+        <v>9.0909090999999997E-2</v>
+      </c>
+      <c r="E125">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C126" t="s">
+        <v>32</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127">
+        <v>0.20833333300000001</v>
+      </c>
+      <c r="E127">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>30</v>
+      </c>
+      <c r="B128" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" t="s">
+        <v>32</v>
+      </c>
+      <c r="D128">
+        <v>9.0909090999999997E-2</v>
+      </c>
+      <c r="E128">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>24</v>
+      </c>
+      <c r="B129" t="s">
+        <v>25</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129">
+        <v>0.47058823500000002</v>
+      </c>
+      <c r="E129">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130">
+        <v>0.14285714299999999</v>
+      </c>
+      <c r="E130">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>20</v>
+      </c>
+      <c r="B131" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131">
+        <v>0.13513513499999999</v>
+      </c>
+      <c r="E131">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132">
+        <v>0.48387096800000001</v>
+      </c>
+      <c r="E132">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>18</v>
+      </c>
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133">
+        <v>0.22727272700000001</v>
+      </c>
+      <c r="E133">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>16</v>
+      </c>
+      <c r="B134" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134">
         <v>0.2</v>
       </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>232</v>
-      </c>
-      <c r="B114" t="s">
-        <v>233</v>
-      </c>
-      <c r="C114" t="s">
-        <v>32</v>
-      </c>
-      <c r="D114">
-        <v>1</v>
-      </c>
-      <c r="E114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>234</v>
-      </c>
-      <c r="B115" t="s">
-        <v>235</v>
-      </c>
-      <c r="C115" t="s">
-        <v>32</v>
-      </c>
-      <c r="D115">
-        <v>0.35294117600000002</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>236</v>
-      </c>
-      <c r="B116" t="s">
-        <v>237</v>
-      </c>
-      <c r="C116" t="s">
-        <v>32</v>
-      </c>
-      <c r="D116">
-        <v>0.15789473700000001</v>
-      </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>238</v>
-      </c>
-      <c r="B117" t="s">
-        <v>239</v>
-      </c>
-      <c r="C117" t="s">
-        <v>7</v>
-      </c>
-      <c r="D117">
-        <v>1</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>240</v>
-      </c>
-      <c r="B118" t="s">
-        <v>241</v>
-      </c>
-      <c r="C118" t="s">
-        <v>99</v>
-      </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>242</v>
-      </c>
-      <c r="B119" t="s">
-        <v>243</v>
-      </c>
-      <c r="C119" t="s">
-        <v>99</v>
-      </c>
-      <c r="D119">
-        <v>1</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>244</v>
-      </c>
-      <c r="B120" t="s">
-        <v>245</v>
-      </c>
-      <c r="C120" t="s">
-        <v>99</v>
-      </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>246</v>
-      </c>
-      <c r="B121" t="s">
-        <v>247</v>
-      </c>
-      <c r="C121" t="s">
-        <v>99</v>
-      </c>
-      <c r="D121">
-        <v>1</v>
-      </c>
-      <c r="E121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>248</v>
-      </c>
-      <c r="B122" t="s">
-        <v>249</v>
-      </c>
-      <c r="C122" t="s">
-        <v>32</v>
-      </c>
-      <c r="D122">
-        <v>0.36</v>
-      </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>250</v>
-      </c>
-      <c r="B123" t="s">
-        <v>251</v>
-      </c>
-      <c r="C123" t="s">
-        <v>99</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>252</v>
-      </c>
-      <c r="B124" t="s">
-        <v>253</v>
-      </c>
-      <c r="C124" t="s">
-        <v>32</v>
-      </c>
-      <c r="D124">
-        <v>0.117647059</v>
-      </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>254</v>
-      </c>
-      <c r="B125" t="s">
-        <v>255</v>
-      </c>
-      <c r="C125" t="s">
-        <v>32</v>
-      </c>
-      <c r="D125">
-        <v>0.2</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>256</v>
-      </c>
-      <c r="B126" t="s">
-        <v>257</v>
-      </c>
-      <c r="C126" t="s">
-        <v>32</v>
-      </c>
-      <c r="D126">
-        <v>0.130434783</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>258</v>
-      </c>
-      <c r="B127" t="s">
-        <v>259</v>
-      </c>
-      <c r="C127" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127">
-        <v>0.368421053</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>260</v>
-      </c>
-      <c r="B128" t="s">
-        <v>261</v>
-      </c>
-      <c r="C128" t="s">
-        <v>7</v>
-      </c>
-      <c r="D128">
-        <v>0.17647058800000001</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>262</v>
-      </c>
-      <c r="B129" t="s">
-        <v>263</v>
-      </c>
-      <c r="C129" t="s">
-        <v>7</v>
-      </c>
-      <c r="D129">
-        <v>0.4</v>
-      </c>
-      <c r="E129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>264</v>
-      </c>
-      <c r="B130" t="s">
-        <v>265</v>
-      </c>
-      <c r="C130" t="s">
-        <v>32</v>
-      </c>
-      <c r="D130">
-        <v>0.32</v>
-      </c>
-      <c r="E130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>266</v>
-      </c>
-      <c r="B131" t="s">
-        <v>267</v>
-      </c>
-      <c r="C131" t="s">
-        <v>32</v>
-      </c>
-      <c r="D131">
-        <v>0.31818181800000001</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>268</v>
-      </c>
-      <c r="B132" t="s">
-        <v>269</v>
-      </c>
-      <c r="C132" t="s">
-        <v>32</v>
-      </c>
-      <c r="D132">
-        <v>1</v>
-      </c>
-      <c r="E132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>270</v>
-      </c>
-      <c r="B133" t="s">
-        <v>271</v>
-      </c>
-      <c r="C133" t="s">
-        <v>99</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>272</v>
-      </c>
-      <c r="B134" t="s">
-        <v>273</v>
-      </c>
-      <c r="C134" t="s">
-        <v>32</v>
-      </c>
-      <c r="D134">
-        <v>0.25</v>
-      </c>
       <c r="E134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>275</v>
+        <v>15</v>
       </c>
       <c r="C135" t="s">
         <v>7</v>
       </c>
       <c r="D135">
-        <v>0.5</v>
+        <v>3.5714285999999998E-2</v>
       </c>
       <c r="E135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>276</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>277</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D136">
-        <v>0.26315789499999998</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="B137" t="s">
-        <v>279</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D137">
-        <v>8.3333332999999996E-2</v>
+        <v>4.7619047999999997E-2</v>
       </c>
       <c r="E137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>281</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>0.28571428599999998</v>
       </c>
       <c r="E138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>282</v>
+        <v>5</v>
       </c>
       <c r="B139" t="s">
-        <v>283</v>
+        <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D139">
-        <v>0.17391304299999999</v>
+        <v>0.3</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
